--- a/outputs/Block5B_Senate_Model_Flips.xlsx
+++ b/outputs/Block5B_Senate_Model_Flips.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="80">
   <si>
     <t>STATE</t>
   </si>
@@ -196,12 +196,12 @@
     <t>Ohio</t>
   </si>
   <si>
-    <t>Maine</t>
-  </si>
-  <si>
     <t>Alaska</t>
   </si>
   <si>
+    <t>Texas</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -241,9 +241,6 @@
     <t>R+5</t>
   </si>
   <si>
-    <t>D+4</t>
-  </si>
-  <si>
     <t>R+6</t>
   </si>
   <si>
@@ -253,10 +250,10 @@
     <t>Appointed (2025)[p]</t>
   </si>
   <si>
-    <t>50.98% R</t>
-  </si>
-  <si>
     <t>53.90% R</t>
+  </si>
+  <si>
+    <t>53.51% R</t>
   </si>
 </sst>
 </file>
@@ -801,13 +798,13 @@
         <v>62</v>
       </c>
       <c r="C2">
-        <v>51.45</v>
+        <v>49.92</v>
       </c>
       <c r="D2">
-        <v>43.42</v>
+        <v>41.4</v>
       </c>
       <c r="E2">
-        <v>8.02</v>
+        <v>8.52</v>
       </c>
       <c r="F2" t="s">
         <v>63</v>
@@ -819,22 +816,22 @@
         <v>67</v>
       </c>
       <c r="I2">
-        <v>54.23</v>
+        <v>54.67</v>
       </c>
       <c r="J2">
-        <v>45.77</v>
+        <v>45.33</v>
       </c>
       <c r="K2">
-        <v>8.460000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="L2">
-        <v>-0.3</v>
+        <v>-0.18</v>
       </c>
       <c r="M2">
-        <v>8.16</v>
+        <v>9.16</v>
       </c>
       <c r="N2">
-        <v>8.16</v>
+        <v>9.16</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -843,25 +840,25 @@
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>54.08</v>
+        <v>54.58</v>
       </c>
       <c r="R2">
-        <v>45.92</v>
+        <v>45.42</v>
       </c>
       <c r="S2">
-        <v>-0.3</v>
+        <v>-0.18</v>
       </c>
       <c r="T2">
-        <v>8.16</v>
+        <v>9.16</v>
       </c>
       <c r="U2">
-        <v>8.16</v>
+        <v>9.16</v>
       </c>
       <c r="V2">
-        <v>89.66</v>
+        <v>91.81</v>
       </c>
       <c r="W2">
-        <v>10.34</v>
+        <v>8.19</v>
       </c>
       <c r="X2" t="s">
         <v>65</v>
@@ -879,28 +876,28 @@
         <v>71</v>
       </c>
       <c r="AC2">
-        <v>89.66</v>
+        <v>91.81</v>
       </c>
       <c r="AD2" t="s">
         <v>72</v>
       </c>
       <c r="AE2">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF2">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG2">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH2">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI2">
+        <v>3.51</v>
+      </c>
+      <c r="AJ2">
         <v>3.24</v>
-      </c>
-      <c r="AJ2">
-        <v>2.9</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -912,7 +909,7 @@
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AO2" t="s">
         <v>62</v>
@@ -924,25 +921,25 @@
         <v>2.620000000000005</v>
       </c>
       <c r="AR2">
-        <v>9.15573551212689</v>
+        <v>10.15789243716453</v>
       </c>
       <c r="AS2">
-        <v>5.535735512126886</v>
+        <v>6.53789243716453</v>
       </c>
       <c r="AT2">
-        <v>7.345735512126888</v>
+        <v>8.347892437164532</v>
       </c>
       <c r="AU2">
-        <v>1.836433878031722</v>
+        <v>2.086973109291133</v>
       </c>
       <c r="AV2">
         <v>4.53</v>
       </c>
       <c r="AW2">
-        <v>5.67</v>
+        <v>5.8</v>
       </c>
       <c r="AX2">
-        <v>6.46</v>
+        <v>6.58</v>
       </c>
       <c r="AY2">
         <v>1.11</v>
@@ -977,13 +974,13 @@
         <v>62</v>
       </c>
       <c r="C3">
-        <v>49.92</v>
+        <v>48.4</v>
       </c>
       <c r="D3">
-        <v>46.55</v>
+        <v>44.82</v>
       </c>
       <c r="E3">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="F3" t="s">
         <v>64</v>
@@ -995,22 +992,22 @@
         <v>68</v>
       </c>
       <c r="I3">
-        <v>51.75</v>
+        <v>51.92</v>
       </c>
       <c r="J3">
-        <v>48.25</v>
+        <v>48.08</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="L3">
-        <v>-0.47</v>
+        <v>-0.3</v>
       </c>
       <c r="M3">
-        <v>3.03</v>
+        <v>3.54</v>
       </c>
       <c r="N3">
-        <v>3.03</v>
+        <v>3.54</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1019,25 +1016,25 @@
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>51.51</v>
+        <v>51.77</v>
       </c>
       <c r="R3">
-        <v>48.49</v>
+        <v>48.23</v>
       </c>
       <c r="S3">
-        <v>-0.47</v>
+        <v>-0.3</v>
       </c>
       <c r="T3">
-        <v>3.03</v>
+        <v>3.54</v>
       </c>
       <c r="U3">
-        <v>3.03</v>
+        <v>3.54</v>
       </c>
       <c r="V3">
-        <v>68.7</v>
+        <v>71.27</v>
       </c>
       <c r="W3">
-        <v>31.3</v>
+        <v>28.73</v>
       </c>
       <c r="X3" t="s">
         <v>66</v>
@@ -1055,28 +1052,28 @@
         <v>71</v>
       </c>
       <c r="AC3">
-        <v>68.7</v>
+        <v>71.27</v>
       </c>
       <c r="AD3" t="s">
         <v>72</v>
       </c>
       <c r="AE3">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF3">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG3">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH3">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI3">
+        <v>3.51</v>
+      </c>
+      <c r="AJ3">
         <v>3.24</v>
-      </c>
-      <c r="AJ3">
-        <v>2.9</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -1088,25 +1085,25 @@
         <v>-5</v>
       </c>
       <c r="AN3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AR3">
-        <v>8.027335204854857</v>
+        <v>8.536611196062932</v>
       </c>
       <c r="AT3">
-        <v>8.027335204854857</v>
+        <v>8.536611196062932</v>
       </c>
       <c r="AU3">
-        <v>2.006833801213714</v>
+        <v>2.134152799015733</v>
       </c>
       <c r="AV3">
         <v>4.15</v>
       </c>
       <c r="AW3">
-        <v>5.39</v>
+        <v>5.49</v>
       </c>
       <c r="AX3">
-        <v>6.21</v>
+        <v>6.3</v>
       </c>
       <c r="AY3">
         <v>1.11</v>
@@ -1141,13 +1138,13 @@
         <v>62</v>
       </c>
       <c r="C4">
-        <v>49.4</v>
+        <v>50.15</v>
       </c>
       <c r="D4">
-        <v>47.7</v>
+        <v>48.38</v>
       </c>
       <c r="E4">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="F4" t="s">
         <v>64</v>
@@ -1159,22 +1156,22 @@
         <v>68</v>
       </c>
       <c r="I4">
-        <v>50.88</v>
+        <v>50.9</v>
       </c>
       <c r="J4">
-        <v>49.12</v>
+        <v>49.1</v>
       </c>
       <c r="K4">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="L4">
-        <v>-0.5</v>
+        <v>2.04</v>
       </c>
       <c r="M4">
-        <v>1.25</v>
+        <v>3.84</v>
       </c>
       <c r="N4">
-        <v>1.25</v>
+        <v>3.84</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1183,25 +1180,25 @@
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>50.63</v>
+        <v>50.58</v>
       </c>
       <c r="R4">
-        <v>49.37</v>
+        <v>49.42</v>
       </c>
       <c r="S4">
-        <v>-0.5</v>
+        <v>2.04</v>
       </c>
       <c r="T4">
-        <v>1.25</v>
+        <v>3.84</v>
       </c>
       <c r="U4">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V4">
-        <v>56.37</v>
+        <v>56.21</v>
       </c>
       <c r="W4">
-        <v>43.63</v>
+        <v>43.79</v>
       </c>
       <c r="X4" t="s">
         <v>66</v>
@@ -1219,28 +1216,28 @@
         <v>71</v>
       </c>
       <c r="AC4">
-        <v>56.37</v>
+        <v>56.21</v>
       </c>
       <c r="AD4" t="s">
         <v>72</v>
       </c>
       <c r="AE4">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF4">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG4">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH4">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI4">
+        <v>3.51</v>
+      </c>
+      <c r="AJ4">
         <v>3.24</v>
-      </c>
-      <c r="AJ4">
-        <v>2.9</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -1249,40 +1246,40 @@
         <v>75</v>
       </c>
       <c r="AM4">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="AN4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AO4" t="s">
         <v>62</v>
       </c>
       <c r="AP4">
-        <v>0.5097999999999999</v>
+        <v>0.539</v>
       </c>
       <c r="AQ4">
-        <v>-1.95999999999998</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR4">
-        <v>2.74770982501213</v>
+        <v>9.840986553974432</v>
       </c>
       <c r="AS4">
-        <v>3.212290174987849</v>
+        <v>11.64098655397444</v>
       </c>
       <c r="AT4">
-        <v>2.97999999999999</v>
+        <v>10.74098655397444</v>
       </c>
       <c r="AU4">
-        <v>0.7449999999999974</v>
+        <v>2.685246638493609</v>
       </c>
       <c r="AV4">
-        <v>6.17</v>
+        <v>5.31</v>
       </c>
       <c r="AW4">
-        <v>7.17</v>
+        <v>6.76</v>
       </c>
       <c r="AX4">
-        <v>7.8</v>
+        <v>7.43</v>
       </c>
       <c r="AY4">
         <v>1.11</v>
@@ -1291,22 +1288,22 @@
         <v>3</v>
       </c>
       <c r="BA4">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="BB4">
-        <v>1.02</v>
+        <v>-4.01</v>
       </c>
       <c r="BC4">
-        <v>7.45</v>
+        <v>11.42</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>42.06</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>23.64</v>
       </c>
       <c r="BF4">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1317,13 +1314,13 @@
         <v>62</v>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>48.42</v>
       </c>
       <c r="D5">
-        <v>48.52</v>
+        <v>45.85</v>
       </c>
       <c r="E5">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="F5" t="s">
         <v>64</v>
@@ -1335,22 +1332,22 @@
         <v>68</v>
       </c>
       <c r="I5">
-        <v>50.75</v>
+        <v>51.37</v>
       </c>
       <c r="J5">
-        <v>49.25</v>
+        <v>48.63</v>
       </c>
       <c r="K5">
-        <v>1.5</v>
+        <v>2.73</v>
       </c>
       <c r="L5">
-        <v>0.19</v>
+        <v>0.02</v>
       </c>
       <c r="M5">
-        <v>1.69</v>
+        <v>2.76</v>
       </c>
       <c r="N5">
-        <v>1.69</v>
+        <v>2.76</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1359,25 +1356,25 @@
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>50.32</v>
+        <v>50.19</v>
       </c>
       <c r="R5">
-        <v>49.68</v>
+        <v>49.81</v>
       </c>
       <c r="S5">
-        <v>0.19</v>
+        <v>0.02</v>
       </c>
       <c r="T5">
-        <v>1.69</v>
+        <v>2.76</v>
       </c>
       <c r="U5">
-        <v>0.64</v>
+        <v>0.37</v>
       </c>
       <c r="V5">
-        <v>53.53</v>
+        <v>52.35</v>
       </c>
       <c r="W5">
-        <v>46.47</v>
+        <v>47.65</v>
       </c>
       <c r="X5" t="s">
         <v>69</v>
@@ -1395,70 +1392,70 @@
         <v>71</v>
       </c>
       <c r="AC5">
-        <v>53.53</v>
+        <v>52.35</v>
       </c>
       <c r="AD5" t="s">
         <v>72</v>
       </c>
       <c r="AE5">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF5">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG5">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH5">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI5">
+        <v>3.51</v>
+      </c>
+      <c r="AJ5">
         <v>3.24</v>
-      </c>
-      <c r="AJ5">
-        <v>2.9</v>
       </c>
       <c r="AK5">
         <v>0</v>
       </c>
       <c r="AL5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AM5">
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO5" t="s">
         <v>62</v>
       </c>
       <c r="AP5">
-        <v>0.539</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ5">
-        <v>-7.800000000000011</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR5">
-        <v>7.686016982113116</v>
+        <v>8.755412717885292</v>
       </c>
       <c r="AS5">
-        <v>9.486016982113126</v>
+        <v>9.775412717885303</v>
       </c>
       <c r="AT5">
-        <v>8.58601698211312</v>
+        <v>9.265412717885297</v>
       </c>
       <c r="AU5">
-        <v>2.14650424552828</v>
+        <v>2.316353179471324</v>
       </c>
       <c r="AV5">
-        <v>5.31</v>
+        <v>4.14</v>
       </c>
       <c r="AW5">
-        <v>6.57</v>
+        <v>5.55</v>
       </c>
       <c r="AX5">
-        <v>7.26</v>
+        <v>6.35</v>
       </c>
       <c r="AY5">
         <v>1.11</v>
@@ -1467,22 +1464,22 @@
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="BB5">
-        <v>-4.01</v>
+        <v>1.35</v>
       </c>
       <c r="BC5">
-        <v>11.42</v>
+        <v>5.75</v>
       </c>
       <c r="BD5">
-        <v>42.06</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>23.64</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5B_Senate_Model_Flips.xlsx
+++ b/outputs/Block5B_Senate_Model_Flips.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="83">
   <si>
     <t>STATE</t>
   </si>
@@ -193,13 +193,16 @@
     <t>North Carolina</t>
   </si>
   <si>
+    <t>Texas</t>
+  </si>
+  <si>
     <t>Ohio</t>
   </si>
   <si>
     <t>Alaska</t>
   </si>
   <si>
-    <t>Texas</t>
+    <t>Maine</t>
   </si>
   <si>
     <t>R</t>
@@ -238,22 +241,28 @@
     <t>R+1</t>
   </si>
   <si>
+    <t>R+6</t>
+  </si>
+  <si>
     <t>R+5</t>
   </si>
   <si>
-    <t>R+6</t>
+    <t>D+4</t>
   </si>
   <si>
     <t>48.69% R</t>
   </si>
   <si>
+    <t>53.51% R</t>
+  </si>
+  <si>
     <t>Appointed (2025)[p]</t>
   </si>
   <si>
     <t>53.90% R</t>
   </si>
   <si>
-    <t>53.51% R</t>
+    <t>50.98% R</t>
   </si>
 </sst>
 </file>
@@ -611,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BF5"/>
+  <dimension ref="A1:BF6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:58">
@@ -795,124 +804,124 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2">
-        <v>49.92</v>
+        <v>50.34999999999999</v>
       </c>
       <c r="D2">
-        <v>41.4</v>
+        <v>42.25</v>
       </c>
       <c r="E2">
-        <v>8.52</v>
+        <v>8.1</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2">
-        <v>54.67</v>
+        <v>54.37365010799135</v>
       </c>
       <c r="J2">
-        <v>45.33</v>
+        <v>45.62634989200864</v>
       </c>
       <c r="K2">
-        <v>9.33</v>
+        <v>8.747300215982712</v>
       </c>
       <c r="L2">
-        <v>-0.18</v>
+        <v>-1.321479089073864</v>
       </c>
       <c r="M2">
-        <v>9.16</v>
+        <v>7.425821126908847</v>
       </c>
       <c r="N2">
-        <v>9.16</v>
+        <v>7.425821126908847</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>54.58</v>
+        <v>53.87809544958866</v>
       </c>
       <c r="R2">
-        <v>45.42</v>
+        <v>46.12190455041134</v>
       </c>
       <c r="S2">
-        <v>-0.18</v>
+        <v>-0.9911093168053986</v>
       </c>
       <c r="T2">
-        <v>9.16</v>
+        <v>7.756190899177313</v>
       </c>
       <c r="U2">
-        <v>9.16</v>
+        <v>7.756190899177313</v>
       </c>
       <c r="V2">
-        <v>91.81</v>
+        <v>93.22560446351913</v>
       </c>
       <c r="W2">
-        <v>8.19</v>
+        <v>6.774395536480871</v>
       </c>
       <c r="X2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Y2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA2" t="s">
         <v>71</v>
       </c>
-      <c r="AA2" t="s">
-        <v>70</v>
-      </c>
       <c r="AB2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC2">
-        <v>91.81</v>
+        <v>93.22560446351913</v>
       </c>
       <c r="AD2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE2">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF2">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>0.5722172308539429</v>
       </c>
       <c r="AL2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AO2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AP2">
         <v>0.4869</v>
@@ -921,49 +930,49 @@
         <v>2.620000000000005</v>
       </c>
       <c r="AR2">
-        <v>10.15789243716453</v>
+        <v>8.756190899177312</v>
       </c>
       <c r="AS2">
-        <v>6.53789243716453</v>
+        <v>5.136190899177309</v>
       </c>
       <c r="AT2">
-        <v>8.347892437164532</v>
+        <v>6.94619089917731</v>
       </c>
       <c r="AU2">
-        <v>2.086973109291133</v>
+        <v>1.736547724794328</v>
       </c>
       <c r="AV2">
-        <v>4.53</v>
+        <v>4.808352845952818</v>
       </c>
       <c r="AW2">
-        <v>5.8</v>
+        <v>4.472531501293391</v>
       </c>
       <c r="AX2">
-        <v>6.58</v>
+        <v>5.195711699028696</v>
       </c>
       <c r="AY2">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ2">
         <v>3</v>
       </c>
       <c r="BA2">
-        <v>2.17</v>
+        <v>2.170415722150866</v>
       </c>
       <c r="BB2">
-        <v>0.28</v>
+        <v>0.275052926652725</v>
       </c>
       <c r="BC2">
-        <v>2.95</v>
+        <v>2.954610092474855</v>
       </c>
       <c r="BD2">
-        <v>30.1</v>
+        <v>30.09640135085562</v>
       </c>
       <c r="BE2">
-        <v>30.1</v>
+        <v>30.09640135085562</v>
       </c>
       <c r="BF2">
-        <v>0.9399999999999999</v>
+        <v>0.9401657373535796</v>
       </c>
     </row>
     <row r="3" spans="1:58">
@@ -971,163 +980,175 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>48.4</v>
+        <v>48.675</v>
       </c>
       <c r="D3">
-        <v>44.82</v>
+        <v>45.65</v>
       </c>
       <c r="E3">
-        <v>3.58</v>
+        <v>3.025</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3">
-        <v>51.92</v>
+        <v>51.60349854227405</v>
       </c>
       <c r="J3">
-        <v>48.08</v>
+        <v>48.39650145772595</v>
       </c>
       <c r="K3">
-        <v>3.83</v>
+        <v>3.206997084548107</v>
       </c>
       <c r="L3">
-        <v>-0.3</v>
+        <v>-1.2681457739171</v>
       </c>
       <c r="M3">
-        <v>3.54</v>
+        <v>1.938851310631006</v>
       </c>
       <c r="N3">
-        <v>3.54</v>
+        <v>1.938851310631006</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>51.77</v>
+        <v>51.12794387705514</v>
       </c>
       <c r="R3">
-        <v>48.23</v>
+        <v>48.87205612294486</v>
       </c>
       <c r="S3">
-        <v>-0.3</v>
+        <v>-0.9511093304378253</v>
       </c>
       <c r="T3">
-        <v>3.54</v>
+        <v>2.255887754110281</v>
       </c>
       <c r="U3">
-        <v>3.54</v>
+        <v>2.255887754110281</v>
       </c>
       <c r="V3">
-        <v>71.27</v>
+        <v>67.08308487070286</v>
       </c>
       <c r="W3">
-        <v>28.73</v>
+        <v>32.91691512929713</v>
       </c>
       <c r="X3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA3" t="s">
         <v>71</v>
       </c>
-      <c r="AA3" t="s">
-        <v>70</v>
-      </c>
       <c r="AB3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC3">
-        <v>71.27</v>
+        <v>67.08308487070286</v>
       </c>
       <c r="AD3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE3">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF3">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>0.549123227957043</v>
       </c>
       <c r="AL3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM3">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AN3" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP3">
+        <v>0.5351</v>
+      </c>
+      <c r="AQ3">
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR3">
-        <v>8.536611196062932</v>
+        <v>8.255887754110281</v>
+      </c>
+      <c r="AS3">
+        <v>9.275887754110292</v>
       </c>
       <c r="AT3">
-        <v>8.536611196062932</v>
+        <v>8.765887754110286</v>
       </c>
       <c r="AU3">
-        <v>2.134152799015733</v>
+        <v>2.191471938527572</v>
       </c>
       <c r="AV3">
-        <v>4.15</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW3">
-        <v>5.49</v>
+        <v>4.362627316035638</v>
       </c>
       <c r="AX3">
-        <v>6.3</v>
+        <v>5.101411483891715</v>
       </c>
       <c r="AY3">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA3">
-        <v>2.8</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB3">
-        <v>0.17</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC3">
-        <v>2.96</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD3">
-        <v>17.49</v>
+        <v>0</v>
       </c>
       <c r="BE3">
         <v>0</v>
       </c>
       <c r="BF3">
-        <v>0.96</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1135,175 +1156,163 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>50.15</v>
+        <v>48.225</v>
       </c>
       <c r="D4">
-        <v>48.38</v>
+        <v>45.1</v>
       </c>
       <c r="E4">
-        <v>1.78</v>
+        <v>3.125</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4">
-        <v>50.9</v>
+        <v>51.67425663005626</v>
       </c>
       <c r="J4">
-        <v>49.1</v>
+        <v>48.32574336994374</v>
       </c>
       <c r="K4">
-        <v>1.8</v>
+        <v>3.348513260112512</v>
       </c>
       <c r="L4">
-        <v>2.04</v>
+        <v>-1.794861267366732</v>
       </c>
       <c r="M4">
-        <v>3.84</v>
+        <v>1.553651992745779</v>
       </c>
       <c r="N4">
-        <v>3.84</v>
+        <v>1.553651992745779</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>50.58</v>
+        <v>51.00118365479373</v>
       </c>
       <c r="R4">
-        <v>49.42</v>
+        <v>48.99881634520627</v>
       </c>
       <c r="S4">
-        <v>2.04</v>
+        <v>-1.346145950525049</v>
       </c>
       <c r="T4">
-        <v>3.84</v>
+        <v>2.002367309587462</v>
       </c>
       <c r="U4">
-        <v>1.16</v>
+        <v>2.002367309587462</v>
       </c>
       <c r="V4">
-        <v>56.21</v>
+        <v>65.26388699510164</v>
       </c>
       <c r="W4">
-        <v>43.79</v>
+        <v>34.73611300489836</v>
       </c>
       <c r="X4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA4" t="s">
         <v>71</v>
       </c>
-      <c r="AA4" t="s">
-        <v>70</v>
-      </c>
       <c r="AB4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC4">
-        <v>56.21</v>
+        <v>65.26388699510164</v>
       </c>
       <c r="AD4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE4">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF4">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>0.7771977269041618</v>
       </c>
       <c r="AL4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM4">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AN4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AP4">
-        <v>0.539</v>
-      </c>
-      <c r="AQ4">
-        <v>-7.800000000000011</v>
+        <v>80</v>
       </c>
       <c r="AR4">
-        <v>9.840986553974432</v>
-      </c>
-      <c r="AS4">
-        <v>11.64098655397444</v>
+        <v>7.002367309587463</v>
       </c>
       <c r="AT4">
-        <v>10.74098655397444</v>
+        <v>7.002367309587463</v>
       </c>
       <c r="AU4">
-        <v>2.685246638493609</v>
+        <v>1.750591827396866</v>
       </c>
       <c r="AV4">
-        <v>5.31</v>
+        <v>4.567515257270437</v>
       </c>
       <c r="AW4">
-        <v>6.76</v>
+        <v>4.363504132448985</v>
       </c>
       <c r="AX4">
-        <v>7.43</v>
+        <v>5.102161340379323</v>
       </c>
       <c r="AY4">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA4">
-        <v>1.54</v>
+        <v>2.797261014127842</v>
       </c>
       <c r="BB4">
-        <v>-4.01</v>
+        <v>0.1730167113317724</v>
       </c>
       <c r="BC4">
-        <v>11.42</v>
+        <v>2.956526743070407</v>
       </c>
       <c r="BD4">
-        <v>42.06</v>
+        <v>17.4915896825486</v>
       </c>
       <c r="BE4">
-        <v>23.64</v>
+        <v>0</v>
       </c>
       <c r="BF4">
-        <v>0.6899999999999999</v>
+        <v>0.956231216651788</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1311,112 +1320,112 @@
         <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>48.42</v>
+        <v>49.325</v>
       </c>
       <c r="D5">
-        <v>45.85</v>
+        <v>47.475</v>
       </c>
       <c r="E5">
-        <v>2.58</v>
+        <v>1.85</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5">
-        <v>51.37</v>
+        <v>50.95557851239669</v>
       </c>
       <c r="J5">
-        <v>48.63</v>
+        <v>49.0444214876033</v>
       </c>
       <c r="K5">
-        <v>2.73</v>
+        <v>1.91115702479339</v>
       </c>
       <c r="L5">
-        <v>0.02</v>
+        <v>-0.1172224213495152</v>
       </c>
       <c r="M5">
-        <v>2.76</v>
+        <v>1.793934603443875</v>
       </c>
       <c r="N5">
-        <v>2.76</v>
+        <v>1.793934603443875</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>50.19</v>
+        <v>50.91162010439063</v>
       </c>
       <c r="R5">
-        <v>49.81</v>
+        <v>49.08837989560937</v>
       </c>
       <c r="S5">
-        <v>0.02</v>
+        <v>-0.08791681601213641</v>
       </c>
       <c r="T5">
-        <v>2.76</v>
+        <v>1.823240208781253</v>
       </c>
       <c r="U5">
-        <v>0.37</v>
+        <v>1.823240208781253</v>
       </c>
       <c r="V5">
-        <v>52.35</v>
+        <v>61.79014903031504</v>
       </c>
       <c r="W5">
-        <v>47.65</v>
+        <v>38.20985096968496</v>
       </c>
       <c r="X5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Y5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA5" t="s">
         <v>71</v>
       </c>
-      <c r="AA5" t="s">
-        <v>70</v>
-      </c>
       <c r="AB5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC5">
-        <v>52.35</v>
+        <v>61.79014903031504</v>
       </c>
       <c r="AD5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE5">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF5">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>0.05075879739090176</v>
       </c>
       <c r="AL5" t="s">
         <v>75</v>
@@ -1425,61 +1434,237 @@
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AO5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AP5">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ5">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR5">
-        <v>8.755412717885292</v>
+        <v>7.823240208781254</v>
       </c>
       <c r="AS5">
-        <v>9.775412717885303</v>
+        <v>9.623240208781265</v>
       </c>
       <c r="AT5">
-        <v>9.265412717885297</v>
+        <v>8.723240208781259</v>
       </c>
       <c r="AU5">
-        <v>2.316353179471324</v>
+        <v>2.180810052195315</v>
       </c>
       <c r="AV5">
-        <v>4.14</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW5">
-        <v>5.55</v>
+        <v>5.472672171724974</v>
       </c>
       <c r="AX5">
-        <v>6.35</v>
+        <v>6.077994959568073</v>
       </c>
       <c r="AY5">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ5">
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.93</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB5">
-        <v>1.35</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC5">
-        <v>5.75</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF5">
-        <v>0.9399999999999999</v>
+        <v>0.6873186760847522</v>
+      </c>
+    </row>
+    <row r="6" spans="1:58">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6">
+        <v>48.25</v>
+      </c>
+      <c r="D6">
+        <v>46.575</v>
+      </c>
+      <c r="E6">
+        <v>1.675</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6">
+        <v>50.8832059056156</v>
+      </c>
+      <c r="J6">
+        <v>49.11679409438439</v>
+      </c>
+      <c r="K6">
+        <v>1.766411811231215</v>
+      </c>
+      <c r="L6">
+        <v>-1.225993544904167</v>
+      </c>
+      <c r="M6">
+        <v>0.5404182663270487</v>
+      </c>
+      <c r="N6">
+        <v>0.5404182663270487</v>
+      </c>
+      <c r="O6">
+        <v>0.25</v>
+      </c>
+      <c r="P6">
+        <v>0.75</v>
+      </c>
+      <c r="Q6">
+        <v>50.42345832627655</v>
+      </c>
+      <c r="R6">
+        <v>49.57654167372345</v>
+      </c>
+      <c r="S6">
+        <v>-0.9194951586781249</v>
+      </c>
+      <c r="T6">
+        <v>0.8469166525530903</v>
+      </c>
+      <c r="U6">
+        <v>0.8469166525530903</v>
+      </c>
+      <c r="V6">
+        <v>55.65418073718285</v>
+      </c>
+      <c r="W6">
+        <v>44.34581926281715</v>
+      </c>
+      <c r="X6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC6">
+        <v>55.65418073718285</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE6">
+        <v>8.73527450544567</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0.530870777381373</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM6">
+        <v>4</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP6">
+        <v>0.5097999999999999</v>
+      </c>
+      <c r="AQ6">
+        <v>-1.95999999999998</v>
+      </c>
+      <c r="AR6">
+        <v>3.15308334744691</v>
+      </c>
+      <c r="AS6">
+        <v>2.80691665255307</v>
+      </c>
+      <c r="AT6">
+        <v>2.97999999999999</v>
+      </c>
+      <c r="AU6">
+        <v>0.7449999999999974</v>
+      </c>
+      <c r="AV6">
+        <v>6.166256775636249</v>
+      </c>
+      <c r="AW6">
+        <v>5.33631557212084</v>
+      </c>
+      <c r="AX6">
+        <v>5.955513908523875</v>
+      </c>
+      <c r="AY6">
+        <v>0.8436468628413508</v>
+      </c>
+      <c r="AZ6">
+        <v>3</v>
+      </c>
+      <c r="BA6">
+        <v>1.878161728442779</v>
+      </c>
+      <c r="BB6">
+        <v>1.021885173756878</v>
+      </c>
+      <c r="BC6">
+        <v>7.445671083211828</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0.9207631564477893</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5B_Senate_Model_Flips.xlsx
+++ b/outputs/Block5B_Senate_Model_Flips.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
   <si>
     <t>STATE</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Lean</t>
+  </si>
+  <si>
+    <t>D Tilt</t>
   </si>
   <si>
     <t>Toss-Up</t>
@@ -873,22 +876,22 @@
         <v>66</v>
       </c>
       <c r="Y2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA2" t="s">
         <v>72</v>
       </c>
-      <c r="AA2" t="s">
-        <v>71</v>
-      </c>
       <c r="AB2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC2">
         <v>93.22560446351913</v>
       </c>
       <c r="AD2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE2">
         <v>8.73527450544567</v>
@@ -912,13 +915,13 @@
         <v>0.5722172308539429</v>
       </c>
       <c r="AL2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO2" t="s">
         <v>63</v>
@@ -1046,25 +1049,25 @@
         <v>32.91691512929713</v>
       </c>
       <c r="X3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Y3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA3" t="s">
         <v>72</v>
       </c>
-      <c r="AA3" t="s">
-        <v>71</v>
-      </c>
       <c r="AB3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC3">
         <v>67.08308487070286</v>
       </c>
       <c r="AD3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE3">
         <v>8.73527450544567</v>
@@ -1088,13 +1091,13 @@
         <v>0.549123227957043</v>
       </c>
       <c r="AL3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM3">
         <v>-6</v>
       </c>
       <c r="AN3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="s">
         <v>63</v>
@@ -1222,25 +1225,25 @@
         <v>34.73611300489836</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Y4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA4" t="s">
         <v>72</v>
       </c>
-      <c r="AA4" t="s">
-        <v>71</v>
-      </c>
       <c r="AB4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC4">
         <v>65.26388699510164</v>
       </c>
       <c r="AD4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE4">
         <v>8.73527450544567</v>
@@ -1264,13 +1267,13 @@
         <v>0.7771977269041618</v>
       </c>
       <c r="AL4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM4">
         <v>-5</v>
       </c>
       <c r="AN4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AR4">
         <v>7.002367309587463</v>
@@ -1386,25 +1389,25 @@
         <v>38.20985096968496</v>
       </c>
       <c r="X5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Y5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA5" t="s">
         <v>72</v>
       </c>
-      <c r="AA5" t="s">
-        <v>71</v>
-      </c>
       <c r="AB5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC5">
         <v>61.79014903031504</v>
       </c>
       <c r="AD5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE5">
         <v>8.73527450544567</v>
@@ -1428,13 +1431,13 @@
         <v>0.05075879739090176</v>
       </c>
       <c r="AL5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM5">
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO5" t="s">
         <v>63</v>
@@ -1562,25 +1565,25 @@
         <v>44.34581926281715</v>
       </c>
       <c r="X6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA6" t="s">
         <v>72</v>
       </c>
-      <c r="AA6" t="s">
-        <v>71</v>
-      </c>
       <c r="AB6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC6">
         <v>55.65418073718285</v>
       </c>
       <c r="AD6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE6">
         <v>8.73527450544567</v>
@@ -1604,13 +1607,13 @@
         <v>0.530870777381373</v>
       </c>
       <c r="AL6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM6">
         <v>4</v>
       </c>
       <c r="AN6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO6" t="s">
         <v>63</v>

--- a/outputs/Block5B_Senate_Model_Flips.xlsx
+++ b/outputs/Block5B_Senate_Model_Flips.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="83">
   <si>
     <t>STATE</t>
   </si>
@@ -193,15 +193,15 @@
     <t>North Carolina</t>
   </si>
   <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
     <t>Texas</t>
   </si>
   <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Alaska</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
@@ -229,9 +229,6 @@
     <t>D Tilt</t>
   </si>
   <si>
-    <t>Toss-Up</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -256,13 +253,13 @@
     <t>48.69% R</t>
   </si>
   <si>
+    <t>53.90% R</t>
+  </si>
+  <si>
+    <t>Appointed (2025)[p]</t>
+  </si>
+  <si>
     <t>53.51% R</t>
-  </si>
-  <si>
-    <t>Appointed (2025)[p]</t>
-  </si>
-  <si>
-    <t>53.90% R</t>
   </si>
   <si>
     <t>50.98% R</t>
@@ -810,13 +807,13 @@
         <v>63</v>
       </c>
       <c r="C2">
-        <v>50.34999999999999</v>
+        <v>50.675</v>
       </c>
       <c r="D2">
-        <v>42.25</v>
+        <v>41.45</v>
       </c>
       <c r="E2">
-        <v>8.1</v>
+        <v>9.225</v>
       </c>
       <c r="F2" t="s">
         <v>64</v>
@@ -828,22 +825,22 @@
         <v>68</v>
       </c>
       <c r="I2">
-        <v>54.37365010799135</v>
+        <v>55.0067842605156</v>
       </c>
       <c r="J2">
-        <v>45.62634989200864</v>
+        <v>44.9932157394844</v>
       </c>
       <c r="K2">
-        <v>8.747300215982712</v>
+        <v>10.0135685210312</v>
       </c>
       <c r="L2">
-        <v>-1.321479089073864</v>
+        <v>-1.380307966940977</v>
       </c>
       <c r="M2">
-        <v>7.425821126908847</v>
+        <v>8.633260554090226</v>
       </c>
       <c r="N2">
-        <v>7.425821126908847</v>
+        <v>8.633260554090226</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -852,76 +849,76 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>53.87809544958866</v>
+        <v>54.48916877291273</v>
       </c>
       <c r="R2">
-        <v>46.12190455041134</v>
+        <v>45.51083122708727</v>
       </c>
       <c r="S2">
-        <v>-0.9911093168053986</v>
+        <v>-1.035230975205733</v>
       </c>
       <c r="T2">
-        <v>7.756190899177313</v>
+        <v>8.97833754582547</v>
       </c>
       <c r="U2">
-        <v>7.756190899177313</v>
+        <v>8.97833754582547</v>
       </c>
       <c r="V2">
-        <v>93.22560446351913</v>
+        <v>95.47518279599674</v>
       </c>
       <c r="W2">
-        <v>6.774395536480871</v>
+        <v>4.52481720400325</v>
       </c>
       <c r="X2" t="s">
         <v>66</v>
       </c>
       <c r="Y2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z2" t="s">
         <v>72</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC2">
+        <v>95.47518279599674</v>
+      </c>
+      <c r="AD2" t="s">
         <v>73</v>
       </c>
-      <c r="AA2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC2">
-        <v>93.22560446351913</v>
-      </c>
-      <c r="AD2" t="s">
+      <c r="AE2">
+        <v>8.719769247836687</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0.5976908822084687</v>
+      </c>
+      <c r="AL2" t="s">
         <v>74</v>
-      </c>
-      <c r="AE2">
-        <v>8.73527450544567</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0.5722172308539429</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>75</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AO2" t="s">
         <v>63</v>
@@ -933,25 +930,25 @@
         <v>2.620000000000005</v>
       </c>
       <c r="AR2">
-        <v>8.756190899177312</v>
+        <v>9.97833754582547</v>
       </c>
       <c r="AS2">
-        <v>5.136190899177309</v>
+        <v>6.358337545825465</v>
       </c>
       <c r="AT2">
-        <v>6.94619089917731</v>
+        <v>8.168337545825468</v>
       </c>
       <c r="AU2">
-        <v>1.736547724794328</v>
+        <v>2.042084386456367</v>
       </c>
       <c r="AV2">
         <v>4.808352845952818</v>
       </c>
       <c r="AW2">
-        <v>4.472531501293391</v>
+        <v>4.597750331251065</v>
       </c>
       <c r="AX2">
-        <v>5.195711699028696</v>
+        <v>5.303884438586613</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -986,13 +983,13 @@
         <v>63</v>
       </c>
       <c r="C3">
-        <v>48.675</v>
+        <v>50.55</v>
       </c>
       <c r="D3">
-        <v>45.65</v>
+        <v>48.25</v>
       </c>
       <c r="E3">
-        <v>3.025</v>
+        <v>2.3</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
@@ -1004,22 +1001,22 @@
         <v>69</v>
       </c>
       <c r="I3">
-        <v>51.60349854227405</v>
+        <v>51.16396761133603</v>
       </c>
       <c r="J3">
-        <v>48.39650145772595</v>
+        <v>48.83603238866397</v>
       </c>
       <c r="K3">
-        <v>3.206997084548107</v>
+        <v>2.327935222672068</v>
       </c>
       <c r="L3">
-        <v>-1.2681457739171</v>
+        <v>1.046950541341876</v>
       </c>
       <c r="M3">
-        <v>1.938851310631006</v>
+        <v>3.374885764013944</v>
       </c>
       <c r="N3">
-        <v>1.938851310631006</v>
+        <v>3.374885764013944</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1028,49 +1025,49 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>51.12794387705514</v>
+        <v>51.55657406433924</v>
       </c>
       <c r="R3">
-        <v>48.87205612294486</v>
+        <v>48.44342593566076</v>
       </c>
       <c r="S3">
-        <v>-0.9511093304378253</v>
+        <v>0.7852129060064073</v>
       </c>
       <c r="T3">
-        <v>2.255887754110281</v>
+        <v>3.113148128678475</v>
       </c>
       <c r="U3">
-        <v>2.255887754110281</v>
+        <v>3.113148128678475</v>
       </c>
       <c r="V3">
-        <v>67.08308487070286</v>
+        <v>69.21939506969498</v>
       </c>
       <c r="W3">
-        <v>32.91691512929713</v>
+        <v>30.78060493030502</v>
       </c>
       <c r="X3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="Y3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z3" t="s">
         <v>72</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC3">
+        <v>69.21939506969498</v>
+      </c>
+      <c r="AD3" t="s">
         <v>73</v>
       </c>
-      <c r="AA3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC3">
-        <v>67.08308487070286</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>74</v>
-      </c>
       <c r="AE3">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1088,46 +1085,46 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>0.549123227957043</v>
+        <v>0.4533428826539674</v>
       </c>
       <c r="AL3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AM3">
         <v>-6</v>
       </c>
       <c r="AN3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO3" t="s">
         <v>63</v>
       </c>
       <c r="AP3">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ3">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR3">
-        <v>8.255887754110281</v>
+        <v>9.113148128678475</v>
       </c>
       <c r="AS3">
-        <v>9.275887754110292</v>
+        <v>10.91314812867849</v>
       </c>
       <c r="AT3">
-        <v>8.765887754110286</v>
+        <v>10.01314812867848</v>
       </c>
       <c r="AU3">
-        <v>2.191471938527572</v>
+        <v>2.50328703216962</v>
       </c>
       <c r="AV3">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW3">
-        <v>4.362627316035638</v>
+        <v>5.60843385395642</v>
       </c>
       <c r="AX3">
-        <v>5.101411483891715</v>
+        <v>6.200517101304247</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
@@ -1136,22 +1133,22 @@
         <v>3</v>
       </c>
       <c r="BA3">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB3">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC3">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF3">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1162,13 +1159,13 @@
         <v>63</v>
       </c>
       <c r="C4">
-        <v>48.225</v>
+        <v>47.8</v>
       </c>
       <c r="D4">
-        <v>45.1</v>
+        <v>43.7</v>
       </c>
       <c r="E4">
-        <v>3.125</v>
+        <v>4.100000000000001</v>
       </c>
       <c r="F4" t="s">
         <v>65</v>
@@ -1180,22 +1177,22 @@
         <v>69</v>
       </c>
       <c r="I4">
-        <v>51.67425663005626</v>
+        <v>52.24043715846994</v>
       </c>
       <c r="J4">
-        <v>48.32574336994374</v>
+        <v>47.75956284153006</v>
       </c>
       <c r="K4">
-        <v>3.348513260112512</v>
+        <v>4.480874316939889</v>
       </c>
       <c r="L4">
-        <v>-1.794861267366732</v>
+        <v>-2.617231028609809</v>
       </c>
       <c r="M4">
-        <v>1.553651992745779</v>
+        <v>1.86364328833008</v>
       </c>
       <c r="N4">
-        <v>1.553651992745779</v>
+        <v>1.86364328833008</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1204,49 +1201,49 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>51.00118365479373</v>
+        <v>51.25897552274127</v>
       </c>
       <c r="R4">
-        <v>48.99881634520627</v>
+        <v>48.74102447725873</v>
       </c>
       <c r="S4">
-        <v>-1.346145950525049</v>
+        <v>-1.962923271457357</v>
       </c>
       <c r="T4">
-        <v>2.002367309587462</v>
+        <v>2.517951045482532</v>
       </c>
       <c r="U4">
-        <v>2.002367309587462</v>
+        <v>2.517951045482532</v>
       </c>
       <c r="V4">
-        <v>65.26388699510164</v>
+        <v>68.55458229868631</v>
       </c>
       <c r="W4">
-        <v>34.73611300489836</v>
+        <v>31.44541770131368</v>
       </c>
       <c r="X4" t="s">
         <v>70</v>
       </c>
       <c r="Y4" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z4" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC4">
+        <v>68.55458229868631</v>
+      </c>
+      <c r="AD4" t="s">
         <v>73</v>
       </c>
-      <c r="AA4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC4">
-        <v>65.26388699510164</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>74</v>
-      </c>
       <c r="AE4">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1264,34 +1261,34 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>0.7771977269041618</v>
+        <v>1.133294279174486</v>
       </c>
       <c r="AL4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM4">
         <v>-5</v>
       </c>
       <c r="AN4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AR4">
-        <v>7.002367309587463</v>
+        <v>7.517951045482532</v>
       </c>
       <c r="AT4">
-        <v>7.002367309587463</v>
+        <v>7.517951045482532</v>
       </c>
       <c r="AU4">
-        <v>1.750591827396866</v>
+        <v>1.879487761370633</v>
       </c>
       <c r="AV4">
         <v>4.567515257270437</v>
       </c>
       <c r="AW4">
-        <v>4.363504132448985</v>
+        <v>4.489472846184185</v>
       </c>
       <c r="AX4">
-        <v>5.102161340379323</v>
+        <v>5.210302147283503</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
@@ -1326,13 +1323,13 @@
         <v>63</v>
       </c>
       <c r="C5">
-        <v>49.325</v>
+        <v>48.675</v>
       </c>
       <c r="D5">
-        <v>47.475</v>
+        <v>46.1</v>
       </c>
       <c r="E5">
-        <v>1.85</v>
+        <v>2.575</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -1344,22 +1341,22 @@
         <v>69</v>
       </c>
       <c r="I5">
-        <v>50.95557851239669</v>
+        <v>51.35848061197573</v>
       </c>
       <c r="J5">
-        <v>49.0444214876033</v>
+        <v>48.64151938802426</v>
       </c>
       <c r="K5">
-        <v>1.91115702479339</v>
+        <v>2.716961223951465</v>
       </c>
       <c r="L5">
-        <v>-0.1172224213495152</v>
+        <v>-1.102239597745279</v>
       </c>
       <c r="M5">
-        <v>1.793934603443875</v>
+        <v>1.614721626206186</v>
       </c>
       <c r="N5">
-        <v>1.793934603443875</v>
+        <v>1.614721626206186</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1368,49 +1365,49 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>50.91162010439063</v>
+        <v>50.94514076282125</v>
       </c>
       <c r="R5">
-        <v>49.08837989560937</v>
+        <v>49.05485923717875</v>
       </c>
       <c r="S5">
-        <v>-0.08791681601213641</v>
+        <v>-0.8266796983089593</v>
       </c>
       <c r="T5">
-        <v>1.823240208781253</v>
+        <v>1.890281525642506</v>
       </c>
       <c r="U5">
-        <v>1.823240208781253</v>
+        <v>1.890281525642506</v>
       </c>
       <c r="V5">
-        <v>61.79014903031504</v>
+        <v>64.5725196739622</v>
       </c>
       <c r="W5">
-        <v>38.20985096968496</v>
+        <v>35.4274803260378</v>
       </c>
       <c r="X5" t="s">
         <v>70</v>
       </c>
       <c r="Y5" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z5" t="s">
         <v>72</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC5">
+        <v>64.5725196739622</v>
+      </c>
+      <c r="AD5" t="s">
         <v>73</v>
       </c>
-      <c r="AA5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC5">
-        <v>61.79014903031504</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>74</v>
-      </c>
       <c r="AE5">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1428,46 +1425,46 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.05075879739090176</v>
+        <v>0.4772837463522762</v>
       </c>
       <c r="AL5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AM5">
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AO5" t="s">
         <v>63</v>
       </c>
       <c r="AP5">
-        <v>0.539</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ5">
-        <v>-7.800000000000011</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR5">
-        <v>7.823240208781254</v>
+        <v>7.890281525642505</v>
       </c>
       <c r="AS5">
-        <v>9.623240208781265</v>
+        <v>8.910281525642516</v>
       </c>
       <c r="AT5">
-        <v>8.723240208781259</v>
+        <v>8.400281525642511</v>
       </c>
       <c r="AU5">
-        <v>2.180810052195315</v>
+        <v>2.100070381410628</v>
       </c>
       <c r="AV5">
-        <v>5.898436507750732</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW5">
-        <v>5.472672171724974</v>
+        <v>4.310457345837744</v>
       </c>
       <c r="AX5">
-        <v>6.077994959568073</v>
+        <v>5.056869047112899</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1476,22 +1473,22 @@
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.541161542643699</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB5">
-        <v>-4.006524474852094</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC5">
-        <v>11.41694912221213</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD5">
-        <v>42.06393827345702</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>0.6873186760847522</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1502,13 +1499,13 @@
         <v>63</v>
       </c>
       <c r="C6">
-        <v>48.25</v>
+        <v>48.825</v>
       </c>
       <c r="D6">
-        <v>46.575</v>
+        <v>47.5</v>
       </c>
       <c r="E6">
-        <v>1.675</v>
+        <v>1.325</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
@@ -1520,22 +1517,22 @@
         <v>69</v>
       </c>
       <c r="I6">
-        <v>50.8832059056156</v>
+        <v>50.68777575914871</v>
       </c>
       <c r="J6">
-        <v>49.11679409438439</v>
+        <v>49.31222424085129</v>
       </c>
       <c r="K6">
-        <v>1.766411811231215</v>
+        <v>1.375551518297428</v>
       </c>
       <c r="L6">
-        <v>-1.225993544904167</v>
+        <v>-0.4670255429338032</v>
       </c>
       <c r="M6">
-        <v>0.5404182663270487</v>
+        <v>0.9085259753636247</v>
       </c>
       <c r="N6">
-        <v>0.5404182663270487</v>
+        <v>0.9085259753636247</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1544,49 +1541,49 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>50.42345832627655</v>
+        <v>50.51264118054853</v>
       </c>
       <c r="R6">
-        <v>49.57654167372345</v>
+        <v>49.48735881945147</v>
       </c>
       <c r="S6">
-        <v>-0.9194951586781249</v>
+        <v>-0.3502691572003522</v>
       </c>
       <c r="T6">
-        <v>0.8469166525530903</v>
+        <v>1.025282361097076</v>
       </c>
       <c r="U6">
-        <v>0.8469166525530903</v>
+        <v>1.025282361097076</v>
       </c>
       <c r="V6">
-        <v>55.65418073718285</v>
+        <v>56.86396059822987</v>
       </c>
       <c r="W6">
-        <v>44.34581926281715</v>
+        <v>43.13603940177013</v>
       </c>
       <c r="X6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y6" t="s">
         <v>71</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
         <v>72</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC6">
+        <v>56.86396059822987</v>
+      </c>
+      <c r="AD6" t="s">
         <v>73</v>
       </c>
-      <c r="AA6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC6">
-        <v>55.65418073718285</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>74</v>
-      </c>
       <c r="AE6">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1604,16 +1601,16 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.530870777381373</v>
+        <v>0.2022279921984468</v>
       </c>
       <c r="AL6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AM6">
         <v>4</v>
       </c>
       <c r="AN6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO6" t="s">
         <v>63</v>
@@ -1625,10 +1622,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR6">
-        <v>3.15308334744691</v>
+        <v>2.974717638902924</v>
       </c>
       <c r="AS6">
-        <v>2.80691665255307</v>
+        <v>2.985282361097055</v>
       </c>
       <c r="AT6">
         <v>2.97999999999999</v>
@@ -1640,10 +1637,10 @@
         <v>6.166256775636249</v>
       </c>
       <c r="AW6">
-        <v>5.33631557212084</v>
+        <v>5.307280945654573</v>
       </c>
       <c r="AX6">
-        <v>5.955513908523875</v>
+        <v>5.929512042779748</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>

--- a/outputs/Block5B_Senate_Model_Flips.xlsx
+++ b/outputs/Block5B_Senate_Model_Flips.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
   <si>
     <t>STATE</t>
   </si>
@@ -193,15 +193,15 @@
     <t>North Carolina</t>
   </si>
   <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
     <t>Alaska</t>
   </si>
   <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
@@ -229,6 +229,9 @@
     <t>D Tilt</t>
   </si>
   <si>
+    <t>Toss-Up</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
@@ -241,25 +244,25 @@
     <t>R+1</t>
   </si>
   <si>
+    <t>R+5</t>
+  </si>
+  <si>
     <t>R+6</t>
   </si>
   <si>
-    <t>R+5</t>
-  </si>
-  <si>
     <t>D+4</t>
   </si>
   <si>
     <t>48.69% R</t>
   </si>
   <si>
+    <t>Appointed (2025)[p]</t>
+  </si>
+  <si>
+    <t>53.51% R</t>
+  </si>
+  <si>
     <t>53.90% R</t>
-  </si>
-  <si>
-    <t>Appointed (2025)[p]</t>
-  </si>
-  <si>
-    <t>53.51% R</t>
   </si>
   <si>
     <t>50.98% R</t>
@@ -807,13 +810,13 @@
         <v>63</v>
       </c>
       <c r="C2">
-        <v>50.675</v>
+        <v>50.74999999999999</v>
       </c>
       <c r="D2">
-        <v>41.45</v>
+        <v>41.375</v>
       </c>
       <c r="E2">
-        <v>9.225</v>
+        <v>9.375</v>
       </c>
       <c r="F2" t="s">
         <v>64</v>
@@ -825,22 +828,22 @@
         <v>68</v>
       </c>
       <c r="I2">
-        <v>55.0067842605156</v>
+        <v>55.08819538670284</v>
       </c>
       <c r="J2">
-        <v>44.9932157394844</v>
+        <v>44.91180461329715</v>
       </c>
       <c r="K2">
-        <v>10.0135685210312</v>
+        <v>10.17639077340569</v>
       </c>
       <c r="L2">
-        <v>-1.380307966940977</v>
+        <v>-1.39302597381857</v>
       </c>
       <c r="M2">
-        <v>8.633260554090226</v>
+        <v>8.783364799587122</v>
       </c>
       <c r="N2">
-        <v>8.633260554090226</v>
+        <v>8.783364799587122</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -849,49 +852,49 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>54.48916877291273</v>
+        <v>54.56581064652088</v>
       </c>
       <c r="R2">
-        <v>45.51083122708727</v>
+        <v>45.43418935347912</v>
       </c>
       <c r="S2">
-        <v>-1.035230975205733</v>
+        <v>-1.044769480363929</v>
       </c>
       <c r="T2">
-        <v>8.97833754582547</v>
+        <v>9.131621293041764</v>
       </c>
       <c r="U2">
-        <v>8.97833754582547</v>
+        <v>9.131621293041764</v>
       </c>
       <c r="V2">
-        <v>95.47518279599674</v>
+        <v>95.70206414313375</v>
       </c>
       <c r="W2">
-        <v>4.52481720400325</v>
+        <v>4.297935856866253</v>
       </c>
       <c r="X2" t="s">
         <v>66</v>
       </c>
       <c r="Y2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA2" t="s">
         <v>72</v>
       </c>
-      <c r="AA2" t="s">
-        <v>71</v>
-      </c>
       <c r="AB2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC2">
-        <v>95.47518279599674</v>
+        <v>95.70206414313375</v>
       </c>
       <c r="AD2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE2">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -909,16 +912,16 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.5976908822084687</v>
+        <v>0.6031979407292191</v>
       </c>
       <c r="AL2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO2" t="s">
         <v>63</v>
@@ -930,25 +933,25 @@
         <v>2.620000000000005</v>
       </c>
       <c r="AR2">
-        <v>9.97833754582547</v>
+        <v>10.13162129304176</v>
       </c>
       <c r="AS2">
-        <v>6.358337545825465</v>
+        <v>6.51162129304176</v>
       </c>
       <c r="AT2">
-        <v>8.168337545825468</v>
+        <v>8.321621293041762</v>
       </c>
       <c r="AU2">
-        <v>2.042084386456367</v>
+        <v>2.08040532326044</v>
       </c>
       <c r="AV2">
         <v>4.808352845952818</v>
       </c>
       <c r="AW2">
-        <v>4.597750331251065</v>
+        <v>4.614040001124252</v>
       </c>
       <c r="AX2">
-        <v>5.303884438586613</v>
+        <v>5.318011579654246</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -983,13 +986,13 @@
         <v>63</v>
       </c>
       <c r="C3">
-        <v>50.55</v>
+        <v>47.825</v>
       </c>
       <c r="D3">
-        <v>48.25</v>
+        <v>43.7</v>
       </c>
       <c r="E3">
-        <v>2.3</v>
+        <v>4.125</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
@@ -1001,22 +1004,22 @@
         <v>69</v>
       </c>
       <c r="I3">
-        <v>51.16396761133603</v>
+        <v>52.25348265501229</v>
       </c>
       <c r="J3">
-        <v>48.83603238866397</v>
+        <v>47.74651734498771</v>
       </c>
       <c r="K3">
-        <v>2.327935222672068</v>
+        <v>4.506965310024583</v>
       </c>
       <c r="L3">
-        <v>1.046950541341876</v>
+        <v>-2.638289777369295</v>
       </c>
       <c r="M3">
-        <v>3.374885764013944</v>
+        <v>1.868675532655288</v>
       </c>
       <c r="N3">
-        <v>3.374885764013944</v>
+        <v>1.868675532655288</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1025,49 +1028,49 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>51.55657406433924</v>
+        <v>51.26412398849881</v>
       </c>
       <c r="R3">
-        <v>48.44342593566076</v>
+        <v>48.73587601150119</v>
       </c>
       <c r="S3">
-        <v>0.7852129060064073</v>
+        <v>-1.978717333026971</v>
       </c>
       <c r="T3">
-        <v>3.113148128678475</v>
+        <v>2.528247976997612</v>
       </c>
       <c r="U3">
-        <v>3.113148128678475</v>
+        <v>2.528247976997612</v>
       </c>
       <c r="V3">
-        <v>69.21939506969498</v>
+        <v>68.62056620003455</v>
       </c>
       <c r="W3">
-        <v>30.78060493030502</v>
+        <v>31.37943379996545</v>
       </c>
       <c r="X3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Y3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA3" t="s">
         <v>72</v>
       </c>
-      <c r="AA3" t="s">
-        <v>71</v>
-      </c>
       <c r="AB3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC3">
-        <v>69.21939506969498</v>
+        <v>68.62056620003455</v>
       </c>
       <c r="AD3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE3">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1085,70 +1088,58 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>0.4533428826539674</v>
+        <v>1.1424129848733</v>
       </c>
       <c r="AL3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM3">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AN3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>63</v>
-      </c>
-      <c r="AP3">
-        <v>0.539</v>
-      </c>
-      <c r="AQ3">
-        <v>-7.800000000000011</v>
+        <v>80</v>
       </c>
       <c r="AR3">
-        <v>9.113148128678475</v>
-      </c>
-      <c r="AS3">
-        <v>10.91314812867849</v>
+        <v>7.528247976997612</v>
       </c>
       <c r="AT3">
-        <v>10.01314812867848</v>
+        <v>7.528247976997612</v>
       </c>
       <c r="AU3">
-        <v>2.50328703216962</v>
+        <v>1.882061994249403</v>
       </c>
       <c r="AV3">
-        <v>5.898436507750732</v>
+        <v>4.567515257270437</v>
       </c>
       <c r="AW3">
-        <v>5.60843385395642</v>
+        <v>4.490926033506978</v>
       </c>
       <c r="AX3">
-        <v>6.200517101304247</v>
+        <v>5.211554342784182</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA3">
-        <v>1.541161542643699</v>
+        <v>2.797261014127842</v>
       </c>
       <c r="BB3">
-        <v>-4.006524474852094</v>
+        <v>0.1730167113317724</v>
       </c>
       <c r="BC3">
-        <v>11.41694912221213</v>
+        <v>2.956526743070407</v>
       </c>
       <c r="BD3">
-        <v>42.06393827345702</v>
+        <v>17.4915896825486</v>
       </c>
       <c r="BE3">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF3">
-        <v>0.6873186760847522</v>
+        <v>0.956231216651788</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1159,13 +1150,13 @@
         <v>63</v>
       </c>
       <c r="C4">
-        <v>47.8</v>
+        <v>48.9</v>
       </c>
       <c r="D4">
-        <v>43.7</v>
+        <v>46.175</v>
       </c>
       <c r="E4">
-        <v>4.100000000000001</v>
+        <v>2.725</v>
       </c>
       <c r="F4" t="s">
         <v>65</v>
@@ -1177,22 +1168,22 @@
         <v>69</v>
       </c>
       <c r="I4">
-        <v>52.24043715846994</v>
+        <v>51.43307914804102</v>
       </c>
       <c r="J4">
-        <v>47.75956284153006</v>
+        <v>48.56692085195898</v>
       </c>
       <c r="K4">
-        <v>4.480874316939889</v>
+        <v>2.866158296082041</v>
       </c>
       <c r="L4">
-        <v>-2.617231028609809</v>
+        <v>-0.9522874185159853</v>
       </c>
       <c r="M4">
-        <v>1.86364328833008</v>
+        <v>1.913870877566056</v>
       </c>
       <c r="N4">
-        <v>1.86364328833008</v>
+        <v>1.913870877566056</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1201,49 +1192,49 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>51.25897552274127</v>
+        <v>51.07597136609753</v>
       </c>
       <c r="R4">
-        <v>48.74102447725873</v>
+        <v>48.92402863390247</v>
       </c>
       <c r="S4">
-        <v>-1.962923271457357</v>
+        <v>-0.7142155638869889</v>
       </c>
       <c r="T4">
-        <v>2.517951045482532</v>
+        <v>2.151942732195052</v>
       </c>
       <c r="U4">
-        <v>2.517951045482532</v>
+        <v>2.151942732195052</v>
       </c>
       <c r="V4">
-        <v>68.55458229868631</v>
+        <v>66.42247604555808</v>
       </c>
       <c r="W4">
-        <v>31.44541770131368</v>
+        <v>33.57752395444192</v>
       </c>
       <c r="X4" t="s">
         <v>70</v>
       </c>
       <c r="Y4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA4" t="s">
         <v>72</v>
       </c>
-      <c r="AA4" t="s">
-        <v>71</v>
-      </c>
       <c r="AB4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC4">
-        <v>68.55458229868631</v>
+        <v>66.42247604555808</v>
       </c>
       <c r="AD4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE4">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1261,58 +1252,70 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.133294279174486</v>
+        <v>0.4123525480695734</v>
       </c>
       <c r="AL4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM4">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AN4" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP4">
+        <v>0.5351</v>
+      </c>
+      <c r="AQ4">
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR4">
-        <v>7.517951045482532</v>
+        <v>8.151942732195053</v>
+      </c>
+      <c r="AS4">
+        <v>9.171942732195063</v>
       </c>
       <c r="AT4">
-        <v>7.517951045482532</v>
+        <v>8.661942732195058</v>
       </c>
       <c r="AU4">
-        <v>1.879487761370633</v>
+        <v>2.165485683048765</v>
       </c>
       <c r="AV4">
-        <v>4.567515257270437</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW4">
-        <v>4.489472846184185</v>
+        <v>4.331813166230072</v>
       </c>
       <c r="AX4">
-        <v>5.210302147283503</v>
+        <v>5.075084958548591</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA4">
-        <v>2.797261014127842</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB4">
-        <v>0.1730167113317724</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC4">
-        <v>2.956526743070407</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD4">
-        <v>17.4915896825486</v>
+        <v>0</v>
       </c>
       <c r="BE4">
         <v>0</v>
       </c>
       <c r="BF4">
-        <v>0.956231216651788</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1323,13 +1326,13 @@
         <v>63</v>
       </c>
       <c r="C5">
-        <v>48.675</v>
+        <v>49.475</v>
       </c>
       <c r="D5">
-        <v>46.1</v>
+        <v>46.775</v>
       </c>
       <c r="E5">
-        <v>2.575</v>
+        <v>2.7</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -1341,22 +1344,22 @@
         <v>69</v>
       </c>
       <c r="I5">
-        <v>51.35848061197573</v>
+        <v>51.4025974025974</v>
       </c>
       <c r="J5">
-        <v>48.64151938802426</v>
+        <v>48.5974025974026</v>
       </c>
       <c r="K5">
-        <v>2.716961223951465</v>
+        <v>2.805194805194802</v>
       </c>
       <c r="L5">
-        <v>-1.102239597745279</v>
+        <v>-0.3163895128283701</v>
       </c>
       <c r="M5">
-        <v>1.614721626206186</v>
+        <v>2.488805292366432</v>
       </c>
       <c r="N5">
-        <v>1.614721626206186</v>
+        <v>2.488805292366432</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1365,49 +1368,49 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>50.94514076282125</v>
+        <v>51.28395133528676</v>
       </c>
       <c r="R5">
-        <v>49.05485923717875</v>
+        <v>48.71604866471324</v>
       </c>
       <c r="S5">
-        <v>-0.8266796983089593</v>
+        <v>-0.2372921346212777</v>
       </c>
       <c r="T5">
-        <v>1.890281525642506</v>
+        <v>2.567902670573524</v>
       </c>
       <c r="U5">
-        <v>1.890281525642506</v>
+        <v>2.567902670573524</v>
       </c>
       <c r="V5">
-        <v>64.5725196739622</v>
+        <v>66.19625489789294</v>
       </c>
       <c r="W5">
-        <v>35.4274803260378</v>
+        <v>33.80374510210705</v>
       </c>
       <c r="X5" t="s">
         <v>70</v>
       </c>
       <c r="Y5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA5" t="s">
         <v>72</v>
       </c>
-      <c r="AA5" t="s">
-        <v>71</v>
-      </c>
       <c r="AB5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC5">
-        <v>64.5725196739622</v>
+        <v>66.19625489789294</v>
       </c>
       <c r="AD5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE5">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1425,46 +1428,46 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.4772837463522762</v>
+        <v>0.1370006778001755</v>
       </c>
       <c r="AL5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AM5">
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO5" t="s">
         <v>63</v>
       </c>
       <c r="AP5">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ5">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR5">
-        <v>7.890281525642505</v>
+        <v>8.567902670573524</v>
       </c>
       <c r="AS5">
-        <v>8.910281525642516</v>
+        <v>10.36790267057354</v>
       </c>
       <c r="AT5">
-        <v>8.400281525642511</v>
+        <v>9.46790267057353</v>
       </c>
       <c r="AU5">
-        <v>2.100070381410628</v>
+        <v>2.366975667643382</v>
       </c>
       <c r="AV5">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW5">
-        <v>4.310457345837744</v>
+        <v>5.547966090444774</v>
       </c>
       <c r="AX5">
-        <v>5.056869047112899</v>
+        <v>6.145877461362781</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1473,22 +1476,22 @@
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB5">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC5">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF5">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1499,13 +1502,13 @@
         <v>63</v>
       </c>
       <c r="C6">
-        <v>48.825</v>
+        <v>48.85</v>
       </c>
       <c r="D6">
-        <v>47.5</v>
+        <v>47.55</v>
       </c>
       <c r="E6">
-        <v>1.325</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
@@ -1517,22 +1520,22 @@
         <v>69</v>
       </c>
       <c r="I6">
-        <v>50.68777575914871</v>
+        <v>50.67427385892116</v>
       </c>
       <c r="J6">
-        <v>49.31222424085129</v>
+        <v>49.32572614107884</v>
       </c>
       <c r="K6">
-        <v>1.375551518297428</v>
+        <v>1.348547717842322</v>
       </c>
       <c r="L6">
-        <v>-0.4670255429338032</v>
+        <v>-0.4691798583288631</v>
       </c>
       <c r="M6">
-        <v>0.9085259753636247</v>
+        <v>0.8793678595134593</v>
       </c>
       <c r="N6">
-        <v>0.9085259753636247</v>
+        <v>0.8793678595134593</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1541,49 +1544,49 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>50.51264118054853</v>
+        <v>50.49833141204784</v>
       </c>
       <c r="R6">
-        <v>49.48735881945147</v>
+        <v>49.50166858795216</v>
       </c>
       <c r="S6">
-        <v>-0.3502691572003522</v>
+        <v>-0.3518848937466473</v>
       </c>
       <c r="T6">
-        <v>1.025282361097076</v>
+        <v>0.9966628240956751</v>
       </c>
       <c r="U6">
-        <v>1.025282361097076</v>
+        <v>0.9966628240956751</v>
       </c>
       <c r="V6">
-        <v>56.86396059822987</v>
+        <v>56.67502366776529</v>
       </c>
       <c r="W6">
-        <v>43.13603940177013</v>
+        <v>43.32497633223471</v>
       </c>
       <c r="X6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA6" t="s">
         <v>72</v>
       </c>
-      <c r="AA6" t="s">
-        <v>71</v>
-      </c>
       <c r="AB6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC6">
-        <v>56.86396059822987</v>
+        <v>56.67502366776529</v>
       </c>
       <c r="AD6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE6">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1601,16 +1604,16 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.2022279921984468</v>
+        <v>0.2031608381283897</v>
       </c>
       <c r="AL6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM6">
         <v>4</v>
       </c>
       <c r="AN6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO6" t="s">
         <v>63</v>
@@ -1622,10 +1625,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR6">
-        <v>2.974717638902924</v>
+        <v>3.003337175904325</v>
       </c>
       <c r="AS6">
-        <v>2.985282361097055</v>
+        <v>2.956662824095655</v>
       </c>
       <c r="AT6">
         <v>2.97999999999999</v>
@@ -1637,10 +1640,10 @@
         <v>6.166256775636249</v>
       </c>
       <c r="AW6">
-        <v>5.307280945654573</v>
+        <v>5.306440474313349</v>
       </c>
       <c r="AX6">
-        <v>5.929512042779748</v>
+        <v>5.92875978066179</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>

--- a/outputs/Block5B_Senate_Model_Flips.xlsx
+++ b/outputs/Block5B_Senate_Model_Flips.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="83">
   <si>
     <t>STATE</t>
   </si>
@@ -196,12 +196,12 @@
     <t>Ohio</t>
   </si>
   <si>
+    <t>Alaska</t>
+  </si>
+  <si>
     <t>Texas</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
@@ -229,9 +229,6 @@
     <t>D Tilt</t>
   </si>
   <si>
-    <t>Toss-Up</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -259,10 +256,10 @@
     <t>Appointed (2025)[p]</t>
   </si>
   <si>
+    <t>53.90% R</t>
+  </si>
+  <si>
     <t>53.51% R</t>
-  </si>
-  <si>
-    <t>53.90% R</t>
   </si>
   <si>
     <t>50.98% R</t>
@@ -810,13 +807,13 @@
         <v>63</v>
       </c>
       <c r="C2">
-        <v>50.74999999999999</v>
+        <v>50.64999999999999</v>
       </c>
       <c r="D2">
-        <v>41.375</v>
+        <v>40.84999999999999</v>
       </c>
       <c r="E2">
-        <v>9.375</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F2" t="s">
         <v>64</v>
@@ -828,22 +825,22 @@
         <v>68</v>
       </c>
       <c r="I2">
-        <v>55.08819538670284</v>
+        <v>55.3551912568306</v>
       </c>
       <c r="J2">
-        <v>44.91180461329715</v>
+        <v>44.6448087431694</v>
       </c>
       <c r="K2">
-        <v>10.17639077340569</v>
+        <v>10.7103825136612</v>
       </c>
       <c r="L2">
-        <v>-1.39302597381857</v>
+        <v>-1.555845774894018</v>
       </c>
       <c r="M2">
-        <v>8.783364799587122</v>
+        <v>9.154536738767183</v>
       </c>
       <c r="N2">
-        <v>8.783364799587122</v>
+        <v>9.154536738767183</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -852,76 +849,76 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>54.56581064652088</v>
+        <v>54.77174909124534</v>
       </c>
       <c r="R2">
-        <v>45.43418935347912</v>
+        <v>45.22825090875466</v>
       </c>
       <c r="S2">
-        <v>-1.044769480363929</v>
+        <v>-1.166884331170515</v>
       </c>
       <c r="T2">
-        <v>9.131621293041764</v>
+        <v>9.543498182490687</v>
       </c>
       <c r="U2">
-        <v>9.131621293041764</v>
+        <v>9.543498182490687</v>
       </c>
       <c r="V2">
-        <v>95.70206414313375</v>
+        <v>96.22844716481518</v>
       </c>
       <c r="W2">
-        <v>4.297935856866253</v>
+        <v>3.771552835184822</v>
       </c>
       <c r="X2" t="s">
         <v>66</v>
       </c>
       <c r="Y2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z2" t="s">
         <v>72</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC2">
+        <v>96.22844716481518</v>
+      </c>
+      <c r="AD2" t="s">
         <v>73</v>
       </c>
-      <c r="AA2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC2">
-        <v>95.70206414313375</v>
-      </c>
-      <c r="AD2" t="s">
+      <c r="AE2">
+        <v>9.098901098901106</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0.6737009827144528</v>
+      </c>
+      <c r="AL2" t="s">
         <v>74</v>
-      </c>
-      <c r="AE2">
-        <v>8.452880158905305</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0.6031979407292191</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>75</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AO2" t="s">
         <v>63</v>
@@ -933,25 +930,25 @@
         <v>2.620000000000005</v>
       </c>
       <c r="AR2">
-        <v>10.13162129304176</v>
+        <v>10.54349818249069</v>
       </c>
       <c r="AS2">
-        <v>6.51162129304176</v>
+        <v>6.923498182490682</v>
       </c>
       <c r="AT2">
-        <v>8.321621293041762</v>
+        <v>8.733498182490685</v>
       </c>
       <c r="AU2">
-        <v>2.08040532326044</v>
+        <v>2.183374545622671</v>
       </c>
       <c r="AV2">
         <v>4.808352845952818</v>
       </c>
       <c r="AW2">
-        <v>4.614040001124252</v>
+        <v>4.671621122213203</v>
       </c>
       <c r="AX2">
-        <v>5.318011579654246</v>
+        <v>5.368046752671822</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -986,13 +983,13 @@
         <v>63</v>
       </c>
       <c r="C3">
-        <v>47.825</v>
+        <v>47.675</v>
       </c>
       <c r="D3">
         <v>43.7</v>
       </c>
       <c r="E3">
-        <v>4.125</v>
+        <v>3.975</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
@@ -1004,22 +1001,22 @@
         <v>69</v>
       </c>
       <c r="I3">
-        <v>52.25348265501229</v>
+        <v>52.1751025991792</v>
       </c>
       <c r="J3">
-        <v>47.74651734498771</v>
+        <v>47.8248974008208</v>
       </c>
       <c r="K3">
-        <v>4.506965310024583</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="L3">
-        <v>-2.638289777369295</v>
+        <v>-2.651610263822058</v>
       </c>
       <c r="M3">
-        <v>1.868675532655288</v>
+        <v>1.698594934536351</v>
       </c>
       <c r="N3">
-        <v>1.868675532655288</v>
+        <v>1.698594934536351</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1028,49 +1025,49 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>51.26412398849881</v>
+        <v>51.18074875024593</v>
       </c>
       <c r="R3">
-        <v>48.73587601150119</v>
+        <v>48.81925124975407</v>
       </c>
       <c r="S3">
-        <v>-1.978717333026971</v>
+        <v>-1.988707697866544</v>
       </c>
       <c r="T3">
-        <v>2.528247976997612</v>
+        <v>2.361497500491866</v>
       </c>
       <c r="U3">
-        <v>2.528247976997612</v>
+        <v>2.361497500491866</v>
       </c>
       <c r="V3">
-        <v>68.62056620003455</v>
+        <v>67.5043909927755</v>
       </c>
       <c r="W3">
-        <v>31.37943379996545</v>
+        <v>32.4956090072245</v>
       </c>
       <c r="X3" t="s">
         <v>70</v>
       </c>
       <c r="Y3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z3" t="s">
         <v>72</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC3">
+        <v>67.5043909927755</v>
+      </c>
+      <c r="AD3" t="s">
         <v>73</v>
       </c>
-      <c r="AA3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC3">
-        <v>68.62056620003455</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>74</v>
-      </c>
       <c r="AE3">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1088,34 +1085,34 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.1424129848733</v>
+        <v>1.14818092470273</v>
       </c>
       <c r="AL3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AM3">
         <v>-5</v>
       </c>
       <c r="AN3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR3">
-        <v>7.528247976997612</v>
+        <v>7.361497500491866</v>
       </c>
       <c r="AT3">
-        <v>7.528247976997612</v>
+        <v>7.361497500491866</v>
       </c>
       <c r="AU3">
-        <v>1.882061994249403</v>
+        <v>1.840374375122966</v>
       </c>
       <c r="AV3">
         <v>4.567515257270437</v>
       </c>
       <c r="AW3">
-        <v>4.490926033506978</v>
+        <v>4.480837687014714</v>
       </c>
       <c r="AX3">
-        <v>5.211554342784182</v>
+        <v>5.202863481462234</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
@@ -1150,13 +1147,13 @@
         <v>63</v>
       </c>
       <c r="C4">
-        <v>48.9</v>
+        <v>49.225</v>
       </c>
       <c r="D4">
-        <v>46.175</v>
+        <v>47.025</v>
       </c>
       <c r="E4">
-        <v>2.725</v>
+        <v>2.2</v>
       </c>
       <c r="F4" t="s">
         <v>65</v>
@@ -1168,22 +1165,22 @@
         <v>69</v>
       </c>
       <c r="I4">
-        <v>51.43307914804102</v>
+        <v>51.14285714285715</v>
       </c>
       <c r="J4">
-        <v>48.56692085195898</v>
+        <v>48.85714285714285</v>
       </c>
       <c r="K4">
-        <v>2.866158296082041</v>
+        <v>2.285714285714292</v>
       </c>
       <c r="L4">
-        <v>-0.9522874185159853</v>
+        <v>-0.3058484137633198</v>
       </c>
       <c r="M4">
-        <v>1.913870877566056</v>
+        <v>1.979865871950972</v>
       </c>
       <c r="N4">
-        <v>1.913870877566056</v>
+        <v>1.979865871950972</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1192,49 +1189,49 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>51.07597136609753</v>
+        <v>51.0281639876959</v>
       </c>
       <c r="R4">
-        <v>48.92402863390247</v>
+        <v>48.9718360123041</v>
       </c>
       <c r="S4">
-        <v>-0.7142155638869889</v>
+        <v>-0.2293863103224898</v>
       </c>
       <c r="T4">
-        <v>2.151942732195052</v>
+        <v>2.056327975391802</v>
       </c>
       <c r="U4">
-        <v>2.151942732195052</v>
+        <v>2.056327975391802</v>
       </c>
       <c r="V4">
-        <v>66.42247604555808</v>
+        <v>63.19398747980172</v>
       </c>
       <c r="W4">
-        <v>33.57752395444192</v>
+        <v>36.80601252019828</v>
       </c>
       <c r="X4" t="s">
         <v>70</v>
       </c>
       <c r="Y4" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z4" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC4">
+        <v>63.19398747980172</v>
+      </c>
+      <c r="AD4" t="s">
         <v>73</v>
       </c>
-      <c r="AA4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC4">
-        <v>66.42247604555808</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>74</v>
-      </c>
       <c r="AE4">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1252,46 +1249,46 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>0.4123525480695734</v>
+        <v>0.1324362480131045</v>
       </c>
       <c r="AL4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM4">
         <v>-6</v>
       </c>
       <c r="AN4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AO4" t="s">
         <v>63</v>
       </c>
       <c r="AP4">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ4">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR4">
-        <v>8.151942732195053</v>
+        <v>8.056327975391802</v>
       </c>
       <c r="AS4">
-        <v>9.171942732195063</v>
+        <v>9.856327975391814</v>
       </c>
       <c r="AT4">
-        <v>8.661942732195058</v>
+        <v>8.956327975391808</v>
       </c>
       <c r="AU4">
-        <v>2.165485683048765</v>
+        <v>2.239081993847952</v>
       </c>
       <c r="AV4">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW4">
-        <v>4.331813166230072</v>
+        <v>5.499257889098187</v>
       </c>
       <c r="AX4">
-        <v>5.075084958548591</v>
+        <v>6.101943900116634</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
@@ -1300,22 +1297,22 @@
         <v>3</v>
       </c>
       <c r="BA4">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB4">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC4">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF4">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1326,13 +1323,13 @@
         <v>63</v>
       </c>
       <c r="C5">
-        <v>49.475</v>
+        <v>48.575</v>
       </c>
       <c r="D5">
-        <v>46.775</v>
+        <v>46.3</v>
       </c>
       <c r="E5">
-        <v>2.7</v>
+        <v>2.275</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -1344,22 +1341,22 @@
         <v>69</v>
       </c>
       <c r="I5">
-        <v>51.4025974025974</v>
+        <v>51.19894598155468</v>
       </c>
       <c r="J5">
-        <v>48.5974025974026</v>
+        <v>48.80105401844532</v>
       </c>
       <c r="K5">
-        <v>2.805194805194802</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="L5">
-        <v>-0.3163895128283701</v>
+        <v>-1.043389660304166</v>
       </c>
       <c r="M5">
-        <v>2.488805292366432</v>
+        <v>1.354502302805193</v>
       </c>
       <c r="N5">
-        <v>2.488805292366432</v>
+        <v>1.354502302805193</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1368,49 +1365,49 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>51.28395133528676</v>
+        <v>50.80767485894062</v>
       </c>
       <c r="R5">
-        <v>48.71604866471324</v>
+        <v>49.19232514105938</v>
       </c>
       <c r="S5">
-        <v>-0.2372921346212777</v>
+        <v>-0.7825422452281245</v>
       </c>
       <c r="T5">
-        <v>2.567902670573524</v>
+        <v>1.615349717881234</v>
       </c>
       <c r="U5">
-        <v>2.567902670573524</v>
+        <v>1.615349717881234</v>
       </c>
       <c r="V5">
-        <v>66.19625489789294</v>
+        <v>62.59604325003473</v>
       </c>
       <c r="W5">
-        <v>33.80374510210705</v>
+        <v>37.40395674996527</v>
       </c>
       <c r="X5" t="s">
         <v>70</v>
       </c>
       <c r="Y5" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z5" t="s">
         <v>72</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC5">
+        <v>62.59604325003473</v>
+      </c>
+      <c r="AD5" t="s">
         <v>73</v>
       </c>
-      <c r="AA5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC5">
-        <v>66.19625489789294</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>74</v>
-      </c>
       <c r="AE5">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1428,46 +1425,46 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.1370006778001755</v>
+        <v>0.4518009759347119</v>
       </c>
       <c r="AL5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM5">
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AO5" t="s">
         <v>63</v>
       </c>
       <c r="AP5">
-        <v>0.539</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ5">
-        <v>-7.800000000000011</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR5">
-        <v>8.567902670573524</v>
+        <v>7.615349717881235</v>
       </c>
       <c r="AS5">
-        <v>10.36790267057354</v>
+        <v>8.635349717881244</v>
       </c>
       <c r="AT5">
-        <v>9.46790267057353</v>
+        <v>8.125349717881239</v>
       </c>
       <c r="AU5">
-        <v>2.366975667643382</v>
+        <v>2.03133742947031</v>
       </c>
       <c r="AV5">
-        <v>5.898436507750732</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW5">
-        <v>5.547966090444774</v>
+        <v>4.278349256582922</v>
       </c>
       <c r="AX5">
-        <v>6.145877461362781</v>
+        <v>5.029528247327535</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1476,22 +1473,22 @@
         <v>3</v>
       </c>
       <c r="BA5">
-        <v>1.541161542643699</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB5">
-        <v>-4.006524474852094</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC5">
-        <v>11.41694912221213</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD5">
-        <v>42.06393827345702</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>0.6873186760847522</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1502,13 +1499,13 @@
         <v>63</v>
       </c>
       <c r="C6">
-        <v>48.85</v>
+        <v>49.125</v>
       </c>
       <c r="D6">
-        <v>47.55</v>
+        <v>47.175</v>
       </c>
       <c r="E6">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
@@ -1520,22 +1517,22 @@
         <v>69</v>
       </c>
       <c r="I6">
-        <v>50.67427385892116</v>
+        <v>51.01246105919003</v>
       </c>
       <c r="J6">
-        <v>49.32572614107884</v>
+        <v>48.98753894080997</v>
       </c>
       <c r="K6">
-        <v>1.348547717842322</v>
+        <v>2.024922118380061</v>
       </c>
       <c r="L6">
-        <v>-0.4691798583288631</v>
+        <v>-0.3204838353402772</v>
       </c>
       <c r="M6">
-        <v>0.8793678595134593</v>
+        <v>1.704438283039784</v>
       </c>
       <c r="N6">
-        <v>0.8793678595134593</v>
+        <v>1.704438283039784</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1544,49 +1541,49 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>50.49833141204784</v>
+        <v>50.89227962093743</v>
       </c>
       <c r="R6">
-        <v>49.50166858795216</v>
+        <v>49.10772037906257</v>
       </c>
       <c r="S6">
-        <v>-0.3518848937466473</v>
+        <v>-0.2403628765052079</v>
       </c>
       <c r="T6">
-        <v>0.9966628240956751</v>
+        <v>1.784559241874853</v>
       </c>
       <c r="U6">
-        <v>0.9966628240956751</v>
+        <v>1.784559241874853</v>
       </c>
       <c r="V6">
-        <v>56.67502366776529</v>
+        <v>61.83849093383414</v>
       </c>
       <c r="W6">
-        <v>43.32497633223471</v>
+        <v>38.16150906616586</v>
       </c>
       <c r="X6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y6" t="s">
         <v>71</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
         <v>72</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC6">
+        <v>61.83849093383414</v>
+      </c>
+      <c r="AD6" t="s">
         <v>73</v>
       </c>
-      <c r="AA6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC6">
-        <v>56.67502366776529</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>74</v>
-      </c>
       <c r="AE6">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1604,16 +1601,16 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.2031608381283897</v>
+        <v>0.1387735714534746</v>
       </c>
       <c r="AL6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AM6">
         <v>4</v>
       </c>
       <c r="AN6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AO6" t="s">
         <v>63</v>
@@ -1625,10 +1622,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR6">
-        <v>3.003337175904325</v>
+        <v>2.215440758125147</v>
       </c>
       <c r="AS6">
-        <v>2.956662824095655</v>
+        <v>3.744559241874833</v>
       </c>
       <c r="AT6">
         <v>2.97999999999999</v>
@@ -1640,10 +1637,10 @@
         <v>6.166256775636249</v>
       </c>
       <c r="AW6">
-        <v>5.306440474313349</v>
+        <v>5.301134249610259</v>
       </c>
       <c r="AX6">
-        <v>5.92875978066179</v>
+        <v>5.924011002838607</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>

--- a/outputs/Block5B_Senate_Model_Flips.xlsx
+++ b/outputs/Block5B_Senate_Model_Flips.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
   <si>
     <t>STATE</t>
   </si>
@@ -208,22 +208,25 @@
     <t>R</t>
   </si>
   <si>
-    <t>RSenLikPollLD (&gt;5%&lt;=10%)</t>
+    <t>RSenSafPollLD (&gt;10%)</t>
   </si>
   <si>
     <t>RSenLeanPollLD (&gt;1&lt;=5%)</t>
   </si>
   <si>
+    <t>D Safe</t>
+  </si>
+  <si>
+    <t>D Lean</t>
+  </si>
+  <si>
+    <t>Safe</t>
+  </si>
+  <si>
+    <t>Lean</t>
+  </si>
+  <si>
     <t>D Likely</t>
-  </si>
-  <si>
-    <t>D Lean</t>
-  </si>
-  <si>
-    <t>Likely</t>
-  </si>
-  <si>
-    <t>Lean</t>
   </si>
   <si>
     <t>D Tilt</t>
@@ -807,13 +810,13 @@
         <v>63</v>
       </c>
       <c r="C2">
-        <v>50.64999999999999</v>
+        <v>51.1</v>
       </c>
       <c r="D2">
-        <v>40.84999999999999</v>
+        <v>40.725</v>
       </c>
       <c r="E2">
-        <v>9.800000000000001</v>
+        <v>10.375</v>
       </c>
       <c r="F2" t="s">
         <v>64</v>
@@ -825,22 +828,22 @@
         <v>68</v>
       </c>
       <c r="I2">
-        <v>55.3551912568306</v>
+        <v>55.64933297032398</v>
       </c>
       <c r="J2">
-        <v>44.6448087431694</v>
+        <v>44.35066702967601</v>
       </c>
       <c r="K2">
-        <v>10.7103825136612</v>
+        <v>11.29866594064797</v>
       </c>
       <c r="L2">
-        <v>-1.555845774894018</v>
+        <v>-1.328018485761584</v>
       </c>
       <c r="M2">
-        <v>9.154536738767183</v>
+        <v>9.970647454886388</v>
       </c>
       <c r="N2">
-        <v>9.154536738767183</v>
+        <v>9.970647454886388</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -849,49 +852,49 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>54.77174909124534</v>
+        <v>55.15132603816339</v>
       </c>
       <c r="R2">
-        <v>45.22825090875466</v>
+        <v>44.84867396183661</v>
       </c>
       <c r="S2">
-        <v>-1.166884331170515</v>
+        <v>-0.9960138643211884</v>
       </c>
       <c r="T2">
-        <v>9.543498182490687</v>
+        <v>10.30265207632678</v>
       </c>
       <c r="U2">
-        <v>9.543498182490687</v>
+        <v>10.30265207632678</v>
       </c>
       <c r="V2">
-        <v>96.22844716481518</v>
+        <v>97.10292526103559</v>
       </c>
       <c r="W2">
-        <v>3.771552835184822</v>
+        <v>2.8970747389644</v>
       </c>
       <c r="X2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Y2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA2" t="s">
         <v>72</v>
       </c>
-      <c r="AA2" t="s">
-        <v>71</v>
-      </c>
       <c r="AB2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC2">
-        <v>96.22844716481518</v>
+        <v>97.10292526103559</v>
       </c>
       <c r="AD2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE2">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -909,16 +912,16 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.6737009827144528</v>
+        <v>0.5750488726824372</v>
       </c>
       <c r="AL2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO2" t="s">
         <v>63</v>
@@ -930,25 +933,25 @@
         <v>2.620000000000005</v>
       </c>
       <c r="AR2">
-        <v>10.54349818249069</v>
+        <v>11.30265207632678</v>
       </c>
       <c r="AS2">
-        <v>6.923498182490682</v>
+        <v>7.682652076326779</v>
       </c>
       <c r="AT2">
-        <v>8.733498182490685</v>
+        <v>9.492652076326781</v>
       </c>
       <c r="AU2">
-        <v>2.183374545622671</v>
+        <v>2.373163019081695</v>
       </c>
       <c r="AV2">
         <v>4.808352845952818</v>
       </c>
       <c r="AW2">
-        <v>4.671621122213203</v>
+        <v>4.746671443331257</v>
       </c>
       <c r="AX2">
-        <v>5.368046752671822</v>
+        <v>5.433486157182918</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -983,13 +986,13 @@
         <v>63</v>
       </c>
       <c r="C3">
-        <v>47.675</v>
+        <v>48.125</v>
       </c>
       <c r="D3">
         <v>43.7</v>
       </c>
       <c r="E3">
-        <v>3.975</v>
+        <v>4.425</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
@@ -1001,22 +1004,22 @@
         <v>69</v>
       </c>
       <c r="I3">
-        <v>52.1751025991792</v>
+        <v>52.40947454396951</v>
       </c>
       <c r="J3">
-        <v>47.8248974008208</v>
+        <v>47.59052545603049</v>
       </c>
       <c r="K3">
-        <v>4.35020519835841</v>
+        <v>4.818949087939018</v>
       </c>
       <c r="L3">
-        <v>-2.651610263822058</v>
+        <v>-2.374390711518226</v>
       </c>
       <c r="M3">
-        <v>1.698594934536351</v>
+        <v>2.444558376420792</v>
       </c>
       <c r="N3">
-        <v>1.698594934536351</v>
+        <v>2.444558376420792</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1025,49 +1028,49 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>51.18074875024593</v>
+        <v>51.51907802715017</v>
       </c>
       <c r="R3">
-        <v>48.81925124975407</v>
+        <v>48.48092197284983</v>
       </c>
       <c r="S3">
-        <v>-1.988707697866544</v>
+        <v>-1.78079303363867</v>
       </c>
       <c r="T3">
-        <v>2.361497500491866</v>
+        <v>3.038156054300348</v>
       </c>
       <c r="U3">
-        <v>2.361497500491866</v>
+        <v>3.038156054300348</v>
       </c>
       <c r="V3">
-        <v>67.5043909927755</v>
+        <v>71.91900153246786</v>
       </c>
       <c r="W3">
-        <v>32.4956090072245</v>
+        <v>28.08099846753214</v>
       </c>
       <c r="X3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="Y3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA3" t="s">
         <v>72</v>
       </c>
-      <c r="AA3" t="s">
-        <v>71</v>
-      </c>
       <c r="AB3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC3">
-        <v>67.5043909927755</v>
+        <v>71.91900153246786</v>
       </c>
       <c r="AD3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE3">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1085,34 +1088,34 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.14818092470273</v>
+        <v>1.028141337342296</v>
       </c>
       <c r="AL3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM3">
         <v>-5</v>
       </c>
       <c r="AN3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR3">
-        <v>7.361497500491866</v>
+        <v>8.038156054300348</v>
       </c>
       <c r="AT3">
-        <v>7.361497500491866</v>
+        <v>8.038156054300348</v>
       </c>
       <c r="AU3">
-        <v>1.840374375122966</v>
+        <v>2.009539013575087</v>
       </c>
       <c r="AV3">
         <v>4.567515257270437</v>
       </c>
       <c r="AW3">
-        <v>4.480837687014714</v>
+        <v>4.517251250195202</v>
       </c>
       <c r="AX3">
-        <v>5.202863481462234</v>
+        <v>5.234256478885237</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
@@ -1147,13 +1150,13 @@
         <v>63</v>
       </c>
       <c r="C4">
-        <v>49.225</v>
+        <v>49.45</v>
       </c>
       <c r="D4">
-        <v>47.025</v>
+        <v>47.625</v>
       </c>
       <c r="E4">
-        <v>2.2</v>
+        <v>1.825</v>
       </c>
       <c r="F4" t="s">
         <v>65</v>
@@ -1165,22 +1168,22 @@
         <v>69</v>
       </c>
       <c r="I4">
-        <v>51.14285714285715</v>
+        <v>50.93999484934329</v>
       </c>
       <c r="J4">
-        <v>48.85714285714285</v>
+        <v>49.06000515065671</v>
       </c>
       <c r="K4">
-        <v>2.285714285714292</v>
+        <v>1.879989698686586</v>
       </c>
       <c r="L4">
-        <v>-0.3058484137633198</v>
+        <v>0.03624629882810737</v>
       </c>
       <c r="M4">
-        <v>1.979865871950972</v>
+        <v>1.916235997514693</v>
       </c>
       <c r="N4">
-        <v>1.979865871950972</v>
+        <v>1.916235997514693</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1189,49 +1192,49 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>51.0281639876959</v>
+        <v>50.95358721140384</v>
       </c>
       <c r="R4">
-        <v>48.9718360123041</v>
+        <v>49.04641278859616</v>
       </c>
       <c r="S4">
-        <v>-0.2293863103224898</v>
+        <v>0.02718472412108053</v>
       </c>
       <c r="T4">
-        <v>2.056327975391802</v>
+        <v>1.907174422807667</v>
       </c>
       <c r="U4">
-        <v>2.056327975391802</v>
+        <v>1.907174422807667</v>
       </c>
       <c r="V4">
-        <v>63.19398747980172</v>
+        <v>62.30433719532572</v>
       </c>
       <c r="W4">
-        <v>36.80601252019828</v>
+        <v>37.69566280467428</v>
       </c>
       <c r="X4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA4" t="s">
         <v>72</v>
       </c>
-      <c r="AA4" t="s">
-        <v>71</v>
-      </c>
       <c r="AB4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC4">
-        <v>63.19398747980172</v>
+        <v>62.30433719532572</v>
       </c>
       <c r="AD4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE4">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1249,16 +1252,16 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>0.1324362480131045</v>
+        <v>0.01569510778915155</v>
       </c>
       <c r="AL4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM4">
         <v>-6</v>
       </c>
       <c r="AN4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AO4" t="s">
         <v>63</v>
@@ -1270,25 +1273,25 @@
         <v>-7.800000000000011</v>
       </c>
       <c r="AR4">
-        <v>8.056327975391802</v>
+        <v>7.907174422807667</v>
       </c>
       <c r="AS4">
-        <v>9.856327975391814</v>
+        <v>9.707174422807679</v>
       </c>
       <c r="AT4">
-        <v>8.956327975391808</v>
+        <v>8.807174422807673</v>
       </c>
       <c r="AU4">
-        <v>2.239081993847952</v>
+        <v>2.201793605701918</v>
       </c>
       <c r="AV4">
         <v>5.898436507750732</v>
       </c>
       <c r="AW4">
-        <v>5.499257889098187</v>
+        <v>5.479128204442785</v>
       </c>
       <c r="AX4">
-        <v>6.101943900116634</v>
+        <v>6.083808668102767</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
@@ -1323,13 +1326,13 @@
         <v>63</v>
       </c>
       <c r="C5">
-        <v>48.575</v>
+        <v>48.525</v>
       </c>
       <c r="D5">
-        <v>46.3</v>
+        <v>46.225</v>
       </c>
       <c r="E5">
-        <v>2.275</v>
+        <v>2.3</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -1341,22 +1344,22 @@
         <v>69</v>
       </c>
       <c r="I5">
-        <v>51.19894598155468</v>
+        <v>51.21372031662269</v>
       </c>
       <c r="J5">
-        <v>48.80105401844532</v>
+        <v>48.78627968337731</v>
       </c>
       <c r="K5">
-        <v>2.397891963109359</v>
+        <v>2.427440633245382</v>
       </c>
       <c r="L5">
-        <v>-1.043389660304166</v>
+        <v>-1.153094892366958</v>
       </c>
       <c r="M5">
-        <v>1.354502302805193</v>
+        <v>1.274345740878424</v>
       </c>
       <c r="N5">
-        <v>1.354502302805193</v>
+        <v>1.274345740878424</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1365,49 +1368,49 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>50.80767485894062</v>
+        <v>50.78130973198508</v>
       </c>
       <c r="R5">
-        <v>49.19232514105938</v>
+        <v>49.21869026801492</v>
       </c>
       <c r="S5">
-        <v>-0.7825422452281245</v>
+        <v>-0.8648211692752186</v>
       </c>
       <c r="T5">
-        <v>1.615349717881234</v>
+        <v>1.562619463970164</v>
       </c>
       <c r="U5">
-        <v>1.615349717881234</v>
+        <v>1.562619463970164</v>
       </c>
       <c r="V5">
-        <v>62.59604325003473</v>
+        <v>62.20127145762546</v>
       </c>
       <c r="W5">
-        <v>37.40395674996527</v>
+        <v>37.79872854237454</v>
       </c>
       <c r="X5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA5" t="s">
         <v>72</v>
       </c>
-      <c r="AA5" t="s">
-        <v>71</v>
-      </c>
       <c r="AB5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC5">
-        <v>62.59604325003473</v>
+        <v>62.20127145762546</v>
       </c>
       <c r="AD5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE5">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1425,16 +1428,16 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.4518009759347119</v>
+        <v>0.4993047348819343</v>
       </c>
       <c r="AL5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM5">
         <v>-6</v>
       </c>
       <c r="AN5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO5" t="s">
         <v>63</v>
@@ -1446,25 +1449,25 @@
         <v>-7.02000000000001</v>
       </c>
       <c r="AR5">
-        <v>7.615349717881235</v>
+        <v>7.562619463970163</v>
       </c>
       <c r="AS5">
-        <v>8.635349717881244</v>
+        <v>8.582619463970174</v>
       </c>
       <c r="AT5">
-        <v>8.125349717881239</v>
+        <v>8.072619463970168</v>
       </c>
       <c r="AU5">
-        <v>2.03133742947031</v>
+        <v>2.018154865992542</v>
       </c>
       <c r="AV5">
         <v>4.345503062353619</v>
       </c>
       <c r="AW5">
-        <v>4.278349256582922</v>
+        <v>4.276786783839438</v>
       </c>
       <c r="AX5">
-        <v>5.029528247327535</v>
+        <v>5.02819920287429</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1499,13 +1502,13 @@
         <v>63</v>
       </c>
       <c r="C6">
-        <v>49.125</v>
+        <v>49.075</v>
       </c>
       <c r="D6">
-        <v>47.175</v>
+        <v>47.525</v>
       </c>
       <c r="E6">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
@@ -1517,22 +1520,22 @@
         <v>69</v>
       </c>
       <c r="I6">
-        <v>51.01246105919003</v>
+        <v>50.80227743271222</v>
       </c>
       <c r="J6">
-        <v>48.98753894080997</v>
+        <v>49.19772256728779</v>
       </c>
       <c r="K6">
-        <v>2.024922118380061</v>
+        <v>1.604554865424426</v>
       </c>
       <c r="L6">
-        <v>-0.3204838353402772</v>
+        <v>-0.2692769494406259</v>
       </c>
       <c r="M6">
-        <v>1.704438283039784</v>
+        <v>1.3352779159838</v>
       </c>
       <c r="N6">
-        <v>1.704438283039784</v>
+        <v>1.3352779159838</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1541,49 +1544,49 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>50.89227962093743</v>
+        <v>50.70129857667198</v>
       </c>
       <c r="R6">
-        <v>49.10772037906257</v>
+        <v>49.29870142332802</v>
       </c>
       <c r="S6">
-        <v>-0.2403628765052079</v>
+        <v>-0.2019577120804694</v>
       </c>
       <c r="T6">
-        <v>1.784559241874853</v>
+        <v>1.402597153343956</v>
       </c>
       <c r="U6">
-        <v>1.784559241874853</v>
+        <v>1.402597153343956</v>
       </c>
       <c r="V6">
-        <v>61.83849093383414</v>
+        <v>59.35812758782153</v>
       </c>
       <c r="W6">
-        <v>38.16150906616586</v>
+        <v>40.64187241217847</v>
       </c>
       <c r="X6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA6" t="s">
         <v>72</v>
       </c>
-      <c r="AA6" t="s">
-        <v>71</v>
-      </c>
       <c r="AB6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC6">
-        <v>61.83849093383414</v>
+        <v>59.35812758782153</v>
       </c>
       <c r="AD6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE6">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1601,16 +1604,16 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.1387735714534746</v>
+        <v>0.11660033943458</v>
       </c>
       <c r="AL6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM6">
         <v>4</v>
       </c>
       <c r="AN6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO6" t="s">
         <v>63</v>
@@ -1622,10 +1625,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR6">
-        <v>2.215440758125147</v>
+        <v>2.597402846656044</v>
       </c>
       <c r="AS6">
-        <v>3.744559241874833</v>
+        <v>3.362597153343936</v>
       </c>
       <c r="AT6">
         <v>2.97999999999999</v>
@@ -1637,10 +1640,10 @@
         <v>6.166256775636249</v>
       </c>
       <c r="AW6">
-        <v>5.301134249610259</v>
+        <v>5.30106833087324</v>
       </c>
       <c r="AX6">
-        <v>5.924011002838607</v>
+        <v>5.923952015162611</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>
